--- a/Книга1.xlsx
+++ b/Книга1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\urfu\Реляционные базы данных\total_designing_db_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9238E33B-5812-4531-8819-E37CAE9A4F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F425BEE9-38BB-46FC-90A2-E73E821E77C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BDDAEBB5-5428-45F0-B247-2860D88C65F9}"/>
   </bookViews>
